--- a/data/hyundai_faq.xlsx
+++ b/data/hyundai_faq.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yash\Desktop\Hyundai_chatbot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0673019-A522-495B-92AB-4F2B413BDB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE67805-6B55-446F-AF1C-3D1733FC8001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hyundai_FAQ" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="331">
   <si>
     <t>Question</t>
   </si>
@@ -151,488 +151,886 @@
     <t>What is Hyundai Bluelink technology?</t>
   </si>
   <si>
+    <t>Hyundai Bluelink is a connected car technology platform that provides remote vehicle monitoring, control, and safety features through a smartphone application.</t>
+  </si>
+  <si>
     <t>How do I activate Hyundai Bluelink in my vehicle?</t>
   </si>
   <si>
+    <t>Bluelink can be activated through an authorized Hyundai dealership or by completing the registration process in the Bluelink mobile application.</t>
+  </si>
+  <si>
     <t>Can Hyundai Bluelink track my vehicle location?</t>
   </si>
   <si>
+    <t>Yes, Hyundai Bluelink allows users to track the live location of their vehicle through the mobile application.</t>
+  </si>
+  <si>
     <t>Does Hyundai provide over-the-air software updates?</t>
   </si>
   <si>
+    <t>Yes, selected Hyundai vehicles support over-the-air software updates for certain vehicle systems.</t>
+  </si>
+  <si>
     <t>What electric vehicles are offered by Hyundai?</t>
   </si>
   <si>
+    <t>Hyundai offers electric vehicles such as the Hyundai IONIQ 5 and other EV models depending on the market.</t>
+  </si>
+  <si>
     <t>What is the driving range of Hyundai IONIQ 5?</t>
   </si>
   <si>
+    <t>The Hyundai IONIQ 5 offers a driving range that varies based on battery pack, variant, and driving conditions.</t>
+  </si>
+  <si>
     <t>How long does it take to charge Hyundai IONIQ 5?</t>
   </si>
   <si>
+    <t>Charging time for Hyundai IONIQ 5 depends on the charger type, battery level, and charging conditions.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer fast charging support for electric vehicles?</t>
   </si>
   <si>
+    <t>Yes, Hyundai electric vehicles support DC fast charging technology.</t>
+  </si>
+  <si>
     <t>What battery warranty is provided for Hyundai electric vehicles?</t>
   </si>
   <si>
+    <t>Hyundai provides a separate warranty package for electric vehicle batteries according to company policy.</t>
+  </si>
+  <si>
     <t>Are Hyundai electric vehicles eligible for government incentives?</t>
   </si>
   <si>
+    <t>Government incentives for Hyundai electric vehicles depend on local regulations and applicable schemes.</t>
+  </si>
+  <si>
     <t>What accessories are available for Hyundai Creta?</t>
   </si>
   <si>
+    <t>Hyundai offers accessories such as floor mats, seat covers, spoilers, body kits, and infotainment upgrades for Creta.</t>
+  </si>
+  <si>
     <t>Can I purchase genuine Hyundai accessories online?</t>
   </si>
   <si>
+    <t>Yes, genuine Hyundai accessories can be purchased through authorized dealerships and official channels.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer alloy wheels as accessories?</t>
   </si>
   <si>
+    <t>Yes, Hyundai offers alloy wheels as genuine accessories for selected models.</t>
+  </si>
+  <si>
     <t>What are the benefits of using genuine Hyundai parts?</t>
   </si>
   <si>
+    <t>Genuine Hyundai parts ensure compatibility, reliability, performance, and warranty compliance.</t>
+  </si>
+  <si>
     <t>How can I verify if a Hyundai part is genuine?</t>
   </si>
   <si>
+    <t>Customers can verify genuine parts through authorized dealers and official Hyundai packaging.</t>
+  </si>
+  <si>
     <t>What are the maintenance requirements for Hyundai CNG vehicles?</t>
   </si>
   <si>
+    <t>Hyundai CNG vehicles require periodic inspection of the CNG system and routine maintenance according to service schedules.</t>
+  </si>
+  <si>
     <t>How often should engine oil be changed in a Hyundai vehicle?</t>
   </si>
   <si>
+    <t>Engine oil should be changed according to Hyundai's recommended maintenance schedule.</t>
+  </si>
+  <si>
     <t>What type of fuel is recommended for Hyundai turbo petrol engines?</t>
   </si>
   <si>
+    <t>Hyundai recommends using the fuel grade specified in the owner's manual for turbo petrol engines.</t>
+  </si>
+  <si>
     <t>Can I view my vehicle service history online?</t>
   </si>
   <si>
+    <t>Yes, vehicle service history may be accessible through authorized service centers and digital platforms.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer annual maintenance contracts?</t>
   </si>
   <si>
+    <t>Yes, Hyundai offers annual maintenance contracts for selected vehicles.</t>
+  </si>
+  <si>
     <t>What documents are required during vehicle servicing?</t>
   </si>
   <si>
+    <t>Customers may be required to provide vehicle registration details and service records during servicing.</t>
+  </si>
+  <si>
     <t>How can I update my contact information with Hyundai?</t>
   </si>
   <si>
+    <t>Contact information can be updated through Hyundai customer support or authorized dealerships.</t>
+  </si>
+  <si>
     <t>What should I do if my Hyundai key is lost?</t>
   </si>
   <si>
+    <t>If a Hyundai key is lost, customers should contact an authorized Hyundai service center immediately.</t>
+  </si>
+  <si>
     <t>Can I get a duplicate Hyundai key?</t>
   </si>
   <si>
+    <t>Yes, duplicate Hyundai keys can be obtained through authorized service centers after verification.</t>
+  </si>
+  <si>
     <t>How do I reset the infotainment system in my Hyundai vehicle?</t>
   </si>
   <si>
+    <t>The infotainment system can usually be reset through system settings or according to the owner's manual.</t>
+  </si>
+  <si>
     <t>Does Hyundai provide navigation map updates?</t>
   </si>
   <si>
+    <t>Yes, Hyundai provides navigation map updates for supported infotainment systems.</t>
+  </si>
+  <si>
     <t>How can I update the software of my Hyundai infotainment system?</t>
   </si>
   <si>
+    <t>Infotainment software updates can be performed through authorized service centers or official update methods.</t>
+  </si>
+  <si>
     <t>What should I do if my Hyundai battery is discharged?</t>
   </si>
   <si>
+    <t>If the battery is discharged, customers can seek roadside assistance or battery jump-start support.</t>
+  </si>
+  <si>
     <t>How can I improve the fuel efficiency of my Hyundai vehicle?</t>
   </si>
   <si>
+    <t>Fuel efficiency can be improved through smooth driving habits, proper tyre pressure, and regular maintenance.</t>
+  </si>
+  <si>
     <t>What does the check engine warning light indicate?</t>
   </si>
   <si>
+    <t>The check engine warning light indicates that the vehicle has detected a system fault requiring inspection.</t>
+  </si>
+  <si>
     <t>What should I do if a warning light appears on my dashboard?</t>
   </si>
   <si>
+    <t>Customers should refer to the owner's manual and seek professional inspection if a warning light appears.</t>
+  </si>
+  <si>
     <t>How do I check tyre pressure in my Hyundai vehicle?</t>
   </si>
   <si>
+    <t>Tyre pressure can be checked through the TPMS system or a tyre pressure gauge.</t>
+  </si>
+  <si>
     <t>When should tyres be replaced on a Hyundai vehicle?</t>
   </si>
   <si>
+    <t>Tyres should be replaced when tread depth becomes insufficient or when signs of wear are observed.</t>
+  </si>
+  <si>
     <t>Does Hyundai provide tyre replacement assistance?</t>
   </si>
   <si>
+    <t>Some Hyundai roadside assistance programs may provide tyre-related support services.</t>
+  </si>
+  <si>
     <t>How can I schedule a test drive for a Hyundai vehicle?</t>
   </si>
   <si>
+    <t>A test drive can be scheduled through Hyundai dealerships, the official website, or customer support.</t>
+  </si>
+  <si>
     <t>Can I book a Hyundai vehicle online?</t>
   </si>
   <si>
+    <t>Yes, Hyundai vehicles can be booked online through official channels where available.</t>
+  </si>
+  <si>
     <t>What payment options are available when purchasing a Hyundai vehicle?</t>
   </si>
   <si>
+    <t>Payment options may include cash, financing, loans, and digital payment methods.</t>
+  </si>
+  <si>
     <t>How long is the delivery period for a new Hyundai vehicle?</t>
   </si>
   <si>
+    <t>Vehicle delivery timelines depend on model availability, location, and demand.</t>
+  </si>
+  <si>
     <t>Can I cancel my Hyundai vehicle booking?</t>
   </si>
   <si>
+    <t>Booking cancellation policies depend on Hyundai's terms and dealership policies.</t>
+  </si>
+  <si>
     <t>Does Hyundai provide vehicle exchange services?</t>
   </si>
   <si>
+    <t>Yes, Hyundai offers vehicle exchange programs through participating dealerships.</t>
+  </si>
+  <si>
     <t>How can I check the status of my vehicle booking?</t>
   </si>
   <si>
+    <t>Booking status can be checked through dealerships or customer support channels.</t>
+  </si>
+  <si>
     <t>Can I customize my Hyundai vehicle before delivery?</t>
   </si>
   <si>
+    <t>Customization options depend on the vehicle model and dealership offerings before delivery.</t>
+  </si>
+  <si>
     <t>What insurance options are available for Hyundai vehicles?</t>
   </si>
   <si>
+    <t>Hyundai vehicles can be insured through various insurance plans offered by partner providers.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer cashless insurance claims?</t>
   </si>
   <si>
+    <t>Yes, cashless insurance claim facilities are available through network garages and approved insurers.</t>
+  </si>
+  <si>
     <t>How can I renew my Hyundai vehicle insurance?</t>
   </si>
   <si>
+    <t>Insurance renewal can be completed through Hyundai partners, insurers, or authorized dealerships.</t>
+  </si>
+  <si>
     <t>What should I do after a vehicle accident?</t>
   </si>
   <si>
+    <t>After an accident, ensure safety, inform authorities if required, and contact insurance and Hyundai support services.</t>
+  </si>
+  <si>
     <t>Does Hyundai provide accident repair services?</t>
   </si>
   <si>
+    <t>Yes, Hyundai provides accident repair services through authorized body shops and service centers.</t>
+  </si>
+  <si>
     <t>How do I contact Hyundai Roadside Assistance?</t>
   </si>
   <si>
+    <t>Hyundai Roadside Assistance can be contacted through customer support numbers and official service channels.</t>
+  </si>
+  <si>
     <t>Can Hyundai Roadside Assistance help with a flat tyre?</t>
   </si>
   <si>
+    <t>Yes, roadside assistance can provide support for flat tyre situations.</t>
+  </si>
+  <si>
     <t>Can Hyundai Roadside Assistance provide towing services?</t>
   </si>
   <si>
+    <t>Yes, Hyundai roadside assistance offers towing support under eligible conditions.</t>
+  </si>
+  <si>
     <t>What should I do if I run out of fuel?</t>
   </si>
   <si>
+    <t>Customers should contact roadside assistance if they run out of fuel.</t>
+  </si>
+  <si>
     <t>Can Hyundai assist with battery jump-start services?</t>
   </si>
   <si>
+    <t>Yes, Hyundai roadside assistance may provide battery jump-start services.</t>
+  </si>
+  <si>
     <t>Does Hyundai provide emergency lockout assistance?</t>
   </si>
   <si>
+    <t>Yes, emergency lockout assistance may be available through roadside assistance programs.</t>
+  </si>
+  <si>
     <t>How do I register a complaint with Hyundai customer care?</t>
   </si>
   <si>
+    <t>Complaints can be registered through Hyundai customer care, dealerships, or official support channels.</t>
+  </si>
+  <si>
     <t>How can I provide feedback about Hyundai services?</t>
   </si>
   <si>
+    <t>Customers can provide feedback through surveys, websites, mobile apps, or customer support representatives.</t>
+  </si>
+  <si>
     <t>What is Hyundai's customer care helpline?</t>
   </si>
   <si>
+    <t>Hyundai customer care helpline details are available on official Hyundai websites and service documents.</t>
+  </si>
+  <si>
     <t>Can I contact Hyundai through email support?</t>
   </si>
   <si>
+    <t>Yes, Hyundai customer support can be contacted through email where such support is available.</t>
+  </si>
+  <si>
     <t>How can I find Hyundai service campaigns for my vehicle?</t>
   </si>
   <si>
+    <t>Service campaigns can be checked through authorized service centers or official Hyundai channels.</t>
+  </si>
+  <si>
     <t>Does Hyundai issue vehicle recalls?</t>
   </si>
   <si>
+    <t>Yes, Hyundai may issue recalls when safety or quality concerns are identified.</t>
+  </si>
+  <si>
     <t>How can I check if my Hyundai vehicle is affected by a recall?</t>
   </si>
   <si>
+    <t>Recall status can be verified using vehicle identification details through Hyundai support channels.</t>
+  </si>
+  <si>
     <t>What should I do if my vehicle is included in a recall campaign?</t>
   </si>
   <si>
+    <t>Customers should contact an authorized Hyundai service center if their vehicle is affected by a recall.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer free recall repairs?</t>
   </si>
   <si>
+    <t>Yes, recall-related repairs are generally performed according to Hyundai recall policies.</t>
+  </si>
+  <si>
     <t>What is the recommended tyre size for Hyundai Creta?</t>
   </si>
   <si>
+    <t>The recommended tyre size for Hyundai Creta depends on the variant and wheel configuration.</t>
+  </si>
+  <si>
     <t>What is the fuel tank capacity of Hyundai Venue?</t>
   </si>
   <si>
+    <t>The fuel tank capacity of Hyundai Venue varies slightly depending on the model specification.</t>
+  </si>
+  <si>
     <t>How many airbags are available in Hyundai Exter?</t>
   </si>
   <si>
+    <t>Hyundai Exter offers multiple airbags depending on the selected variant.</t>
+  </si>
+  <si>
     <t>Does Hyundai Verna have a sunroof?</t>
   </si>
   <si>
+    <t>Yes, selected variants of Hyundai Verna are equipped with a sunroof.</t>
+  </si>
+  <si>
     <t>What is the ground clearance of Hyundai Creta?</t>
   </si>
   <si>
+    <t>Hyundai Creta provides ground clearance suitable for urban and highway driving conditions.</t>
+  </si>
+  <si>
     <t>Does Hyundai Alcazar support wireless charging?</t>
   </si>
   <si>
+    <t>Yes, Hyundai Alcazar offers wireless charging in selected variants.</t>
+  </si>
+  <si>
     <t>What safety technologies are available in Hyundai Tucson?</t>
   </si>
   <si>
+    <t>Hyundai Tucson includes advanced safety technologies such as ADAS, collision avoidance systems, and driver assistance features.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer connected car features in all models?</t>
   </si>
   <si>
+    <t>Connected car features are available in selected Hyundai models rather than every model.</t>
+  </si>
+  <si>
     <t>What are the benefits of Hyundai's digital key feature?</t>
   </si>
   <si>
+    <t>The digital key feature allows authorized users to access and operate the vehicle using compatible devices.</t>
+  </si>
+  <si>
     <t>Can multiple users access Hyundai Bluelink services?</t>
   </si>
   <si>
+    <t>Yes, multiple users may be granted access to certain Bluelink services depending on system capabilities.</t>
+  </si>
+  <si>
     <t>How secure is Hyundai Bluelink data?</t>
   </si>
   <si>
+    <t>Hyundai implements security measures to protect user and vehicle data within Bluelink services.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer fleet solutions for businesses?</t>
   </si>
   <si>
+    <t>Yes, Hyundai offers fleet mobility solutions for business customers in selected markets.</t>
+  </si>
+  <si>
     <t>Can companies purchase Hyundai vehicles in bulk?</t>
   </si>
   <si>
+    <t>Yes, companies can purchase Hyundai vehicles in bulk through fleet and corporate sales programs.</t>
+  </si>
+  <si>
     <t>Are there special service packages for corporate customers?</t>
   </si>
   <si>
+    <t>Special maintenance and service packages may be available for corporate customers.</t>
+  </si>
+  <si>
     <t>Does Hyundai offer loyalty benefits to existing customers?</t>
   </si>
   <si>
+    <t>Hyundai may offer loyalty benefits and promotional programs to existing customers.</t>
+  </si>
+  <si>
     <t>How can I transfer ownership of a Hyundai vehicle?</t>
   </si>
   <si>
+    <t>Vehicle ownership transfer can be completed through the appropriate transport authority and supporting documentation.</t>
+  </si>
+  <si>
     <t>What documents are required for vehicle ownership transfer?</t>
   </si>
   <si>
-    <t>Hyundai Bluelink is a connected car technology platform that provides remote vehicle monitoring, control, and safety features through a smartphone application.</t>
-  </si>
-  <si>
-    <t>Bluelink can be activated through an authorized Hyundai dealership or by completing the registration process in the Bluelink mobile application.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai Bluelink allows users to track the live location of their vehicle through the mobile application.</t>
-  </si>
-  <si>
-    <t>Yes, selected Hyundai vehicles support over-the-air software updates for certain vehicle systems.</t>
-  </si>
-  <si>
-    <t>Hyundai offers electric vehicles such as the Hyundai IONIQ 5 and other EV models depending on the market.</t>
-  </si>
-  <si>
-    <t>The Hyundai IONIQ 5 offers a driving range that varies based on battery pack, variant, and driving conditions.</t>
-  </si>
-  <si>
-    <t>Charging time for Hyundai IONIQ 5 depends on the charger type, battery level, and charging conditions.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai electric vehicles support DC fast charging technology.</t>
-  </si>
-  <si>
-    <t>Hyundai provides a separate warranty package for electric vehicle batteries according to company policy.</t>
-  </si>
-  <si>
-    <t>Government incentives for Hyundai electric vehicles depend on local regulations and applicable schemes.</t>
-  </si>
-  <si>
-    <t>Hyundai offers accessories such as floor mats, seat covers, spoilers, body kits, and infotainment upgrades for Creta.</t>
-  </si>
-  <si>
-    <t>Yes, genuine Hyundai accessories can be purchased through authorized dealerships and official channels.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai offers alloy wheels as genuine accessories for selected models.</t>
-  </si>
-  <si>
-    <t>Genuine Hyundai parts ensure compatibility, reliability, performance, and warranty compliance.</t>
-  </si>
-  <si>
-    <t>Customers can verify genuine parts through authorized dealers and official Hyundai packaging.</t>
-  </si>
-  <si>
-    <t>Hyundai CNG vehicles require periodic inspection of the CNG system and routine maintenance according to service schedules.</t>
-  </si>
-  <si>
-    <t>Engine oil should be changed according to Hyundai's recommended maintenance schedule.</t>
-  </si>
-  <si>
-    <t>Hyundai recommends using the fuel grade specified in the owner's manual for turbo petrol engines.</t>
-  </si>
-  <si>
-    <t>Yes, vehicle service history may be accessible through authorized service centers and digital platforms.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai offers annual maintenance contracts for selected vehicles.</t>
-  </si>
-  <si>
-    <t>Customers may be required to provide vehicle registration details and service records during servicing.</t>
-  </si>
-  <si>
-    <t>Contact information can be updated through Hyundai customer support or authorized dealerships.</t>
-  </si>
-  <si>
-    <t>If a Hyundai key is lost, customers should contact an authorized Hyundai service center immediately.</t>
-  </si>
-  <si>
-    <t>Yes, duplicate Hyundai keys can be obtained through authorized service centers after verification.</t>
-  </si>
-  <si>
-    <t>The infotainment system can usually be reset through system settings or according to the owner's manual.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai provides navigation map updates for supported infotainment systems.</t>
-  </si>
-  <si>
-    <t>Infotainment software updates can be performed through authorized service centers or official update methods.</t>
-  </si>
-  <si>
-    <t>If the battery is discharged, customers can seek roadside assistance or battery jump-start support.</t>
-  </si>
-  <si>
-    <t>Fuel efficiency can be improved through smooth driving habits, proper tyre pressure, and regular maintenance.</t>
-  </si>
-  <si>
-    <t>The check engine warning light indicates that the vehicle has detected a system fault requiring inspection.</t>
-  </si>
-  <si>
-    <t>Customers should refer to the owner's manual and seek professional inspection if a warning light appears.</t>
-  </si>
-  <si>
-    <t>Tyre pressure can be checked through the TPMS system or a tyre pressure gauge.</t>
-  </si>
-  <si>
-    <t>Tyres should be replaced when tread depth becomes insufficient or when signs of wear are observed.</t>
-  </si>
-  <si>
-    <t>Some Hyundai roadside assistance programs may provide tyre-related support services.</t>
-  </si>
-  <si>
-    <t>A test drive can be scheduled through Hyundai dealerships, the official website, or customer support.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai vehicles can be booked online through official channels where available.</t>
-  </si>
-  <si>
-    <t>Payment options may include cash, financing, loans, and digital payment methods.</t>
-  </si>
-  <si>
-    <t>Vehicle delivery timelines depend on model availability, location, and demand.</t>
-  </si>
-  <si>
-    <t>Booking cancellation policies depend on Hyundai's terms and dealership policies.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai offers vehicle exchange programs through participating dealerships.</t>
-  </si>
-  <si>
-    <t>Booking status can be checked through dealerships or customer support channels.</t>
-  </si>
-  <si>
-    <t>Customization options depend on the vehicle model and dealership offerings before delivery.</t>
-  </si>
-  <si>
-    <t>Hyundai vehicles can be insured through various insurance plans offered by partner providers.</t>
-  </si>
-  <si>
-    <t>Yes, cashless insurance claim facilities are available through network garages and approved insurers.</t>
-  </si>
-  <si>
-    <t>Insurance renewal can be completed through Hyundai partners, insurers, or authorized dealerships.</t>
-  </si>
-  <si>
-    <t>After an accident, ensure safety, inform authorities if required, and contact insurance and Hyundai support services.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai provides accident repair services through authorized body shops and service centers.</t>
-  </si>
-  <si>
-    <t>Hyundai Roadside Assistance can be contacted through customer support numbers and official service channels.</t>
-  </si>
-  <si>
-    <t>Yes, roadside assistance can provide support for flat tyre situations.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai roadside assistance offers towing support under eligible conditions.</t>
-  </si>
-  <si>
-    <t>Customers should contact roadside assistance if they run out of fuel.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai roadside assistance may provide battery jump-start services.</t>
-  </si>
-  <si>
-    <t>Yes, emergency lockout assistance may be available through roadside assistance programs.</t>
-  </si>
-  <si>
-    <t>Complaints can be registered through Hyundai customer care, dealerships, or official support channels.</t>
-  </si>
-  <si>
-    <t>Customers can provide feedback through surveys, websites, mobile apps, or customer support representatives.</t>
-  </si>
-  <si>
-    <t>Hyundai customer care helpline details are available on official Hyundai websites and service documents.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai customer support can be contacted through email where such support is available.</t>
-  </si>
-  <si>
-    <t>Service campaigns can be checked through authorized service centers or official Hyundai channels.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai may issue recalls when safety or quality concerns are identified.</t>
-  </si>
-  <si>
-    <t>Recall status can be verified using vehicle identification details through Hyundai support channels.</t>
-  </si>
-  <si>
-    <t>Customers should contact an authorized Hyundai service center if their vehicle is affected by a recall.</t>
-  </si>
-  <si>
-    <t>Yes, recall-related repairs are generally performed according to Hyundai recall policies.</t>
-  </si>
-  <si>
-    <t>The recommended tyre size for Hyundai Creta depends on the variant and wheel configuration.</t>
-  </si>
-  <si>
-    <t>The fuel tank capacity of Hyundai Venue varies slightly depending on the model specification.</t>
-  </si>
-  <si>
-    <t>Hyundai Exter offers multiple airbags depending on the selected variant.</t>
-  </si>
-  <si>
-    <t>Yes, selected variants of Hyundai Verna are equipped with a sunroof.</t>
-  </si>
-  <si>
-    <t>Hyundai Creta provides ground clearance suitable for urban and highway driving conditions.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai Alcazar offers wireless charging in selected variants.</t>
-  </si>
-  <si>
-    <t>Hyundai Tucson includes advanced safety technologies such as ADAS, collision avoidance systems, and driver assistance features.</t>
-  </si>
-  <si>
-    <t>Connected car features are available in selected Hyundai models rather than every model.</t>
-  </si>
-  <si>
-    <t>The digital key feature allows authorized users to access and operate the vehicle using compatible devices.</t>
-  </si>
-  <si>
-    <t>Yes, multiple users may be granted access to certain Bluelink services depending on system capabilities.</t>
-  </si>
-  <si>
-    <t>Hyundai implements security measures to protect user and vehicle data within Bluelink services.</t>
-  </si>
-  <si>
-    <t>Yes, Hyundai offers fleet mobility solutions for business customers in selected markets.</t>
-  </si>
-  <si>
-    <t>Yes, companies can purchase Hyundai vehicles in bulk through fleet and corporate sales programs.</t>
-  </si>
-  <si>
-    <t>Special maintenance and service packages may be available for corporate customers.</t>
-  </si>
-  <si>
-    <t>Hyundai may offer loyalty benefits and promotional programs to existing customers.</t>
-  </si>
-  <si>
-    <t>Vehicle ownership transfer can be completed through the appropriate transport authority and supporting documentation.</t>
-  </si>
-  <si>
     <t>Ownership transfer generally requires registration documents, identity proof, insurance documents, and applicable forms.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Creta?</t>
+  </si>
+  <si>
+    <t>The Hyundai Creta delivers approximately 17.4 km/l (petrol MT), up to 18.4 km/l (petrol AT), and around 21.4 km/l (diesel) depending on variant. Mileage may vary with driving conditions.</t>
+  </si>
+  <si>
+    <t>How many seats does Hyundai Creta have?</t>
+  </si>
+  <si>
+    <t>The Hyundai Creta is a 5-seater SUV with comfortable seating for five passengers across all variants.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Creta?</t>
+  </si>
+  <si>
+    <t>Hyundai Creta offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Verna?</t>
+  </si>
+  <si>
+    <t>The Hyundai Verna offers competitive mileage of approximately 18.0 km/l (petrol MT) and up to 20.6 km/l (diesel) depending on variant.</t>
+  </si>
+  <si>
+    <t>How does Hyundai Creta compare with Verna?</t>
+  </si>
+  <si>
+    <t>Hyundai Creta is a compact SUV with higher ground clearance and SUV styling, while Verna is a sedan focused on comfort and highway cruising. Creta suits families wanting SUV road presence; Verna suits those preferring sedan ride and boot space.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Creta and Verna</t>
+  </si>
+  <si>
+    <t>Creta is an SUV with higher ground clearance, bold styling, and 5 seats. Verna is a sedan with a longer boot, sedan comfort, and sporty handling. Choose Creta for SUV practicality; choose Verna for sedan elegance.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Creta and Venue</t>
+  </si>
+  <si>
+    <t>Creta is a mid-size SUV with more cabin space and premium features. Venue is a compact SUV with easier city manoeuvring and lower starting price. Creta suits larger families; Venue suits city-focused buyers.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Venue?</t>
+  </si>
+  <si>
+    <t>Hyundai Venue is a 5-seater compact SUV.</t>
+  </si>
+  <si>
+    <t>What is the starting price of Hyundai Verna?</t>
+  </si>
+  <si>
+    <t>The Hyundai Verna starts at approximately Rs. 10.69 lakh (ex-showroom). Prices vary by city and variant.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Alcazar</t>
+  </si>
+  <si>
+    <t>Hyundai Alcazar is a premium 3-row SUV available in 6-seater and 7-seater configurations, with spacious cabin, advanced features, and strong road presence.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Alcazar?</t>
+  </si>
+  <si>
+    <t>The Hyundai Alcazar delivers approximately 18.1 km/l (petrol MT) and up to 17.5 km/l (diesel MT), depending on variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Tucson?</t>
+  </si>
+  <si>
+    <t>The Hyundai Tucson offers approximately 16.4 km/l (petrol) and 18.4 km/l (diesel), depending on variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai i20?</t>
+  </si>
+  <si>
+    <t>The Hyundai i20 delivers approximately 20.4 km/l (petrol MT) and up to 25.2 km/l (diesel MT), depending on variant.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Creta?</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Creta</t>
+  </si>
+  <si>
+    <t>Hyundai Creta is a popular compact SUV known for bold design, spacious cabin, multiple engine options, and premium features.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Venue?</t>
+  </si>
+  <si>
+    <t>The Hyundai Venue starts at approximately ₹8.5 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Venue</t>
+  </si>
+  <si>
+    <t>Hyundai Venue is a compact SUV with connected car tech, multiple turbo engine options, and city-friendly dimensions.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Verna?</t>
+  </si>
+  <si>
+    <t>The Hyundai Verna starts at approximately ₹11.5 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Verna?</t>
+  </si>
+  <si>
+    <t>Hyundai Verna offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Verna</t>
+  </si>
+  <si>
+    <t>Hyundai Verna is a premium sedan with ADAS on select variants, spacious rear seat, and refined ride quality.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Alcazar?</t>
+  </si>
+  <si>
+    <t>The Hyundai Alcazar starts at approximately ₹16.5 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Tucson?</t>
+  </si>
+  <si>
+    <t>The Hyundai Tucson starts at approximately ₹28 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Tucson?</t>
+  </si>
+  <si>
+    <t>Hyundai Tucson offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Tucson</t>
+  </si>
+  <si>
+    <t>Hyundai Tucson is a premium mid-size SUV with advanced safety, panoramic sunroof options, and powerful petrol/diesel engines.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai i20?</t>
+  </si>
+  <si>
+    <t>The Hyundai i20 starts at approximately ₹7.5 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai i20?</t>
+  </si>
+  <si>
+    <t>Hyundai i20 offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai i20</t>
+  </si>
+  <si>
+    <t>Hyundai i20 is a premium hatchback with sharp styling, connected features, and multiple engine-gearbox options.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Exter?</t>
+  </si>
+  <si>
+    <t>The Hyundai Exter starts at approximately ₹6.5 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Exter?</t>
+  </si>
+  <si>
+    <t>The Hyundai Exter delivers approximately 19.4 km/l (petrol MT) and up to 19.2 km/l (petrol AMT), depending on variant.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Exter?</t>
+  </si>
+  <si>
+    <t>Hyundai Exter offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Exter</t>
+  </si>
+  <si>
+    <t>Hyundai Exter is a compact SUV with outdoor-focused styling, good ground clearance, and efficient petrol engines.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Aura?</t>
+  </si>
+  <si>
+    <t>The Hyundai Aura starts at approximately ₹6.5 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Aura?</t>
+  </si>
+  <si>
+    <t>The Hyundai Aura delivers approximately 20.5 km/l (petrol MT) and up to 25.4 km/l (diesel MT), depending on variant.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Aura?</t>
+  </si>
+  <si>
+    <t>Hyundai Aura offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Aura</t>
+  </si>
+  <si>
+    <t>Hyundai Aura is a compact sedan based on the Grand i10 Nios platform, focused on comfort and fuel efficiency.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Grand I10?</t>
+  </si>
+  <si>
+    <t>The Hyundai Grand i10 starts at approximately ₹6 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Grand I10?</t>
+  </si>
+  <si>
+    <t>The Hyundai Grand i10 delivers approximately 20.7 km/l (petrol MT) and up to 25.4 km/l (diesel MT), depending on variant.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Grand I10?</t>
+  </si>
+  <si>
+    <t>Hyundai Grand i10 offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Grand I10</t>
+  </si>
+  <si>
+    <t>Hyundai Grand i10 is a practical hatchback known for easy city driving, low running costs, and comfortable cabin.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Nios?</t>
+  </si>
+  <si>
+    <t>The Hyundai Grand i10 Nios starts at approximately ₹5.7 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Nios?</t>
+  </si>
+  <si>
+    <t>The Hyundai Grand i10 Nios delivers approximately 20.7 km/l (petrol MT) and up to 25.4 km/l (diesel MT), depending on variant.</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Nios?</t>
+  </si>
+  <si>
+    <t>Hyundai Grand i10 Nios offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Nios</t>
+  </si>
+  <si>
+    <t>Hyundai Grand i10 Nios is a feature-rich hatchback with modern connectivity, efficient engines, and compact dimensions.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Ioniq?</t>
+  </si>
+  <si>
+    <t>The Hyundai Ioniq 5 starts at approximately ₹45 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Ioniq?</t>
+  </si>
+  <si>
+    <t>The Hyundai Ioniq 5 offers an ARAI-rated range of up to 631 km per charge (variant dependent).</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Ioniq?</t>
+  </si>
+  <si>
+    <t>Hyundai Ioniq 5 offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Ioniq</t>
+  </si>
+  <si>
+    <t>Hyundai Ioniq 5 is a premium electric crossover with ultra-fast charging, spacious cabin, and advanced tech features.</t>
+  </si>
+  <si>
+    <t>What is the price of Hyundai Kona?</t>
+  </si>
+  <si>
+    <t>The Hyundai Kona Electric starts at approximately ₹24 lakh (ex-showroom). Prices may vary by city and variant.</t>
+  </si>
+  <si>
+    <t>What is the mileage of Hyundai Kona?</t>
+  </si>
+  <si>
+    <t>The Hyundai Kona Electric offers an ARAI-rated range of up to 452 km per charge (variant dependent).</t>
+  </si>
+  <si>
+    <t>What is the seating capacity of Hyundai Kona?</t>
+  </si>
+  <si>
+    <t>Hyundai Kona Electric offers 5-seat configuration in all variants.</t>
+  </si>
+  <si>
+    <t>Tell me about Hyundai Kona</t>
+  </si>
+  <si>
+    <t>Hyundai Kona Electric is a compact electric SUV with practical range, strong performance, and modern safety features.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Alcazar and Creta</t>
+  </si>
+  <si>
+    <t>Alcazar is a larger 6/7-seater SUV with more cabin space and a third-row option, while Creta is a compact 5-seater SUV. Alcazar suits bigger families; Creta is easier in city traffic and generally more fuel-efficient.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Alcazar and Verna</t>
+  </si>
+  <si>
+    <t>Alcazar is a 3-row SUV with higher seating and ground clearance, while Verna is a sedan focused on comfort and highway cruising. Choose Alcazar for family space; Verna for sedan ride and handling.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Alcazar and Tucson</t>
+  </si>
+  <si>
+    <t>Alcazar offers 6/7 seats at a more accessible price, while Tucson is a premium 5-seater with more power and advanced features. Alcazar is family-focused; Tucson is for buyers wanting a luxury SUV experience.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Alcazar and Venue</t>
+  </si>
+  <si>
+    <t>Alcazar is a full-size 3-row SUV for large families, while Venue is a compact 5-seater SUV for city use. Alcazar provides more space; Venue is easier to park and more affordable.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Tucson and Creta</t>
+  </si>
+  <si>
+    <t>Tucson is a larger premium SUV with more power and features, while Creta is a compact SUV with lower price and easier city driving. Tucson suits premium buyers; Creta suits value-focused SUV buyers.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Tucson and Verna</t>
+  </si>
+  <si>
+    <t>Tucson is a premium SUV with higher ground clearance and AWD options on select variants, while Verna is a sedan with lower running costs and sedan comfort. Choose based on body style preference.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Tucson and Venue</t>
+  </si>
+  <si>
+    <t>Tucson is a mid-size premium SUV, while Venue is a compact SUV. Tucson offers more space and power; Venue is more affordable and city-friendly.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Venue and Verna</t>
+  </si>
+  <si>
+    <t>Venue is a compact SUV with higher ground clearance, while Verna is a sedan with more rear-seat comfort and boot space for highway travel. SUV vs sedan preference is the main difference.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Venue and i20</t>
+  </si>
+  <si>
+    <t>Venue is a compact SUV with higher ride height, while i20 is a premium hatchback with sportier handling. Venue suits rough roads better; i20 is easier to park and often more fuel-efficient.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Exter and Venue</t>
+  </si>
+  <si>
+    <t>Exter is a newer compact SUV with efficient petrol engines, while Venue offers more variant choice and turbo petrol options. Both are 5-seaters; Venue is slightly more feature-rich on top trims.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Exter and Creta</t>
+  </si>
+  <si>
+    <t>Exter is an entry compact SUV, while Creta is a larger premium compact SUV with more engine options and space. Creta costs more but offers a more upmarket experience.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai i20 and Verna</t>
+  </si>
+  <si>
+    <t>i20 is a hatchback suited to city driving, while Verna is a sedan with more rear legroom and boot space. Verna is better for families needing sedan comfort on highways.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Aura and Verna</t>
+  </si>
+  <si>
+    <t>Aura is an affordable compact sedan, while Verna is a premium sedan with more features and power. Aura focuses on value; Verna on comfort and technology.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Nios and Grand I10</t>
+  </si>
+  <si>
+    <t>Grand i10 Nios is the newer hatchback with updated styling and features, while Grand i10 is the earlier generation focused on practicality. Nios is generally preferred for latest tech and design.</t>
+  </si>
+  <si>
+    <t>Compare Hyundai Ioniq and Kona</t>
+  </si>
+  <si>
+    <t>Ioniq 5 is a larger premium EV with longer range and ultra-fast charging, while Kona Electric is a compact EV with lower price. Ioniq 5 suits premium EV buyers; Kona suits city-focused EV users.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -643,7 +1041,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -651,12 +1049,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -959,17 +1375,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.5546875" customWidth="1"/>
+    <col min="1" max="1" width="45.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1138,631 +1554,1159 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>130</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="B54" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="B61" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="B65" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="B66" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="B70" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="B72" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="B73" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="B77" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="B79" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="B84" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="B86" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="B88" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="B89" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="B90" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="B92" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="B94" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>115</v>
+        <v>188</v>
       </c>
       <c r="B95" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="B96" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="B97" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="B98" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="B100" t="s">
         <v>199</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>229</v>
+      </c>
+      <c r="B116" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>231</v>
+      </c>
+      <c r="B117" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>233</v>
+      </c>
+      <c r="B118" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>235</v>
+      </c>
+      <c r="B119" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>237</v>
+      </c>
+      <c r="B120" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>239</v>
+      </c>
+      <c r="B121" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>241</v>
+      </c>
+      <c r="B122" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>243</v>
+      </c>
+      <c r="B123" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>245</v>
+      </c>
+      <c r="B124" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>247</v>
+      </c>
+      <c r="B125" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>249</v>
+      </c>
+      <c r="B126" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>251</v>
+      </c>
+      <c r="B127" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>253</v>
+      </c>
+      <c r="B128" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>255</v>
+      </c>
+      <c r="B129" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>257</v>
+      </c>
+      <c r="B130" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>259</v>
+      </c>
+      <c r="B131" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>261</v>
+      </c>
+      <c r="B132" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>263</v>
+      </c>
+      <c r="B133" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>265</v>
+      </c>
+      <c r="B134" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>267</v>
+      </c>
+      <c r="B135" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>269</v>
+      </c>
+      <c r="B136" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>271</v>
+      </c>
+      <c r="B137" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>273</v>
+      </c>
+      <c r="B138" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>275</v>
+      </c>
+      <c r="B139" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>277</v>
+      </c>
+      <c r="B140" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>279</v>
+      </c>
+      <c r="B141" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>281</v>
+      </c>
+      <c r="B142" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>283</v>
+      </c>
+      <c r="B143" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>285</v>
+      </c>
+      <c r="B144" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>287</v>
+      </c>
+      <c r="B145" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>289</v>
+      </c>
+      <c r="B146" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>291</v>
+      </c>
+      <c r="B147" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>293</v>
+      </c>
+      <c r="B148" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>295</v>
+      </c>
+      <c r="B149" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>297</v>
+      </c>
+      <c r="B150" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>299</v>
+      </c>
+      <c r="B151" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>301</v>
+      </c>
+      <c r="B152" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>303</v>
+      </c>
+      <c r="B153" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>305</v>
+      </c>
+      <c r="B154" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>307</v>
+      </c>
+      <c r="B155" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>309</v>
+      </c>
+      <c r="B156" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>311</v>
+      </c>
+      <c r="B157" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>313</v>
+      </c>
+      <c r="B158" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>315</v>
+      </c>
+      <c r="B159" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>317</v>
+      </c>
+      <c r="B160" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>319</v>
+      </c>
+      <c r="B161" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>321</v>
+      </c>
+      <c r="B162" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>323</v>
+      </c>
+      <c r="B163" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>325</v>
+      </c>
+      <c r="B164" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>327</v>
+      </c>
+      <c r="B165" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>329</v>
+      </c>
+      <c r="B166" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
